--- a/EIANN/data/supplementary_tables/Table_S1_mnist_table.xlsx
+++ b/EIANN/data/supplementary_tables/Table_S1_mnist_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,7 +763,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hebbian</t>
+          <t>Unsup. Hebb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -811,7 +811,8 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hebb (Local RF)</t>
+          <t>Unsup. Hebb
+(Wide H1 + Local RF)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -859,8 +860,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dendritic Temporal 
-Contrast</t>
+          <t>Unsup. BCM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dend Temp Contrast</t>
+          <t>Dend Target Prop</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LDS</t>
+          <t>BCM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -895,20 +895,20 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>94.65 ± 0.17</t>
+          <t>82.11 ± 0.39</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>96.15 ± 0.13</t>
+          <t>77.90 ± 0.68</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fixed DendI 
-(random)</t>
+          <t>Dend. Target Prop
+(Learned DendI, Hebb)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -943,20 +943,20 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>86.80 ± 0.50</t>
+          <t>92.62 ± 0.10</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>87.36 ± 0.59</t>
+          <t>94.29 ± 0.13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Learned DendI 
-(local backprop)</t>
+          <t>Dend. Target Prop.
+(Fixed DendI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -991,20 +991,20 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>94.08 ± 0.11</t>
+          <t>86.80 ± 0.50</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>95.04 ± 0.20</t>
+          <t>87.36 ± 0.59</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dendritic 
-Target Propagation</t>
+          <t>Dend. Target Prop.
+(Learned DendI, BP)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1039,20 +1039,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>92.62 ± 0.10</t>
+          <t>94.08 ± 0.11</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>94.29 ± 0.13</t>
+          <t>95.04 ± 0.20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dendritic Temporal 
-Contrast</t>
+          <t>Sup. Hebb + W Norm.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1067,12 +1066,13 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dend Temp Contrast</t>
+          <t>Dend Target Prop</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LDS</t>
+          <t>Hebb 
++ Weight Norm.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1087,19 +1087,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>94.65 ± 0.17</t>
+          <t>36.39 ± 1.34</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>96.15 ± 0.13</t>
+          <t>34.51 ± 1.36</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sup. Hebb + W Norm.</t>
+          <t>Sup. TCH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1119,8 +1119,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hebb 
-+ Weight Norm.</t>
+          <t>TCH</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1135,20 +1134,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>36.39 ± 1.34</t>
+          <t>90.55 ± 0.30</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>34.51 ± 1.36</t>
+          <t>90.89 ± 0.68</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Temp. Contrastive 
-Hebb</t>
+          <t>Sup. BCM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1168,7 +1166,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TCH</t>
+          <t>BCM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1183,19 +1181,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>90.55 ± 0.30</t>
+          <t>81.10 ± 0.52</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>90.89 ± 0.68</t>
+          <t>68.92 ± 0.89</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>Sup. BTSP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1215,7 +1213,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BCM</t>
+          <t>BTSP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1230,19 +1228,20 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>81.10 ± 0.52</t>
+          <t>93.43 ± 0.10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>68.92 ± 0.89</t>
+          <t>94.08 ± 0.13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BTSP</t>
+          <t>LDS, 
+fixed top-down</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1262,12 +1261,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BTSP</t>
+          <t>LDS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Symmetric (B=Wᵀ)</t>
+          <t>Fixed random</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1277,12 +1276,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>93.43 ± 0.10</t>
+          <t>90.93 ± 0.33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>94.08 ± 0.13</t>
+          <t>92.86 ± 0.19</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1289,7 @@
       <c r="A19" t="inlineStr">
         <is>
           <t>LDS, 
-fixed top-down</t>
+learned top-down</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1315,7 +1314,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fixed random</t>
+          <t>Contr. Hebb + W Norm.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1325,20 +1324,20 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>90.93 ± 0.33</t>
+          <t>92.47 ± 0.13</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>92.86 ± 0.19</t>
+          <t>93.96 ± 0.12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LDS, 
-learned top-down</t>
+          <t>BTSP, 
+fixed top-down</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1358,12 +1357,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LDS</t>
+          <t>BTSP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Contr. Hebb + W Norm.</t>
+          <t>Fixed random</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1373,12 +1372,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>92.47 ± 0.13</t>
+          <t>84.24 ± 0.47</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>93.96 ± 0.12</t>
+          <t>83.32 ± 0.47</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1385,7 @@
       <c r="A21" t="inlineStr">
         <is>
           <t>BTSP, 
-fixed top-down</t>
+learned top-down</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1411,7 +1410,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fixed random</t>
+          <t>Contr. Hebb + W Norm.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1421,58 +1420,10 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>84.24 ± 0.47</t>
+          <t>91.65 ± 0.17</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
-        <is>
-          <t>83.32 ± 0.47</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>BTSP, 
-learned top-down</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Dend EIANN</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Dend Target Prop</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>BTSP</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Contr. Hebb + W Norm.</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Zero</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>91.65 ± 0.17</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>93.50 ± 0.14</t>
         </is>
